--- a/backend/data/uploads/MES/2026-07-25_불량현황.xlsx
+++ b/backend/data/uploads/MES/2026-07-25_불량현황.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sihoo\PythonProject\TestProject\backend\data\uploads\MES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CA7E0CAF-5718-4F62-BA16-18C118270C72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{695DE738-3CAB-4BBA-85C0-F4AD4C65C8AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-30828" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{D5B36685-B4BC-475F-BAEC-0C34DA0885A8}"/>
+    <workbookView xWindow="-30240" yWindow="8376" windowWidth="23040" windowHeight="12012" xr2:uid="{326FE858-3C25-449E-B697-FBB5788B9188}"/>
   </bookViews>
   <sheets>
     <sheet name="불량현황" sheetId="1" r:id="rId1"/>
@@ -492,7 +492,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B721160-87DE-4019-8628-CCAF0CF9FC70}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F003501-36A2-405F-B445-360DAF2C51A0}">
   <dimension ref="B2:U12"/>
   <sheetFormatPr defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
